--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484562_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484562_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.4474</v>
+        <v>6.4555</v>
       </c>
       <c r="E2" t="n">
-        <v>4.5894</v>
+        <v>4.7957</v>
       </c>
       <c r="F2" t="n">
-        <v>1.858</v>
+        <v>1.6598</v>
       </c>
       <c r="G2" t="n">
         <v>4.8013</v>
@@ -610,13 +610,13 @@
         <v>2.0158</v>
       </c>
       <c r="S2" t="n">
-        <v>0.5466</v>
+        <v>0.5547</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0709</v>
+        <v>0.2772</v>
       </c>
       <c r="U2" t="n">
-        <v>0.4757</v>
+        <v>0.2775</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.0765</v>
+        <v>3.2466</v>
       </c>
       <c r="E3" t="n">
-        <v>4.4284</v>
+        <v>4.7719</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.3519</v>
+        <v>-1.5253</v>
       </c>
       <c r="G3" t="n">
         <v>3.7698</v>
@@ -688,13 +688,13 @@
         <v>1.8326</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.0598</v>
+        <v>0.1103</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.2579</v>
+        <v>0.0856</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1981</v>
+        <v>0.0247</v>
       </c>
       <c r="V3" t="n">
         <v>-0.6335</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. SOLBES SORIANO</t>
+          <t>R. CARRION BALLESTER</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.0438</v>
+        <v>2.5538</v>
       </c>
       <c r="E4" t="n">
-        <v>2.0662</v>
+        <v>2.4922</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9775</v>
+        <v>0.0615</v>
       </c>
       <c r="G4" t="n">
-        <v>1.14</v>
+        <v>3.1204</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7042</v>
+        <v>1.1363</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4358</v>
+        <v>1.9842</v>
       </c>
       <c r="J4" t="n">
-        <v>0.8853</v>
+        <v>3.1709</v>
       </c>
       <c r="K4" t="n">
-        <v>0.8018999999999999</v>
+        <v>1.7957</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0833</v>
+        <v>1.3753</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2548</v>
+        <v>-0.0505</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.0977</v>
+        <v>-0.6594</v>
       </c>
       <c r="O4" t="n">
-        <v>0.3525</v>
+        <v>0.6089</v>
       </c>
       <c r="P4" t="n">
-        <v>-1.0995</v>
+        <v>0.733</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.8326</v>
+        <v>-0.3665</v>
       </c>
       <c r="R4" t="n">
-        <v>0.733</v>
+        <v>1.0995</v>
       </c>
       <c r="S4" t="n">
-        <v>2.6813</v>
+        <v>-0.6454</v>
       </c>
       <c r="T4" t="n">
-        <v>2.6916</v>
+        <v>-0.3122</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0103</v>
+        <v>-0.3332</v>
       </c>
       <c r="V4" t="n">
-        <v>0.3219</v>
+        <v>-0.6543</v>
       </c>
       <c r="W4" t="n">
-        <v>0.3219</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-0.6543</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>R. CARRION BALLESTER</t>
+          <t>A. SOLBES SORIANO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.4684</v>
+        <v>1.8051</v>
       </c>
       <c r="E5" t="n">
-        <v>2.3821</v>
+        <v>0.679</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0863</v>
+        <v>1.1262</v>
       </c>
       <c r="G5" t="n">
-        <v>3.1204</v>
+        <v>1.14</v>
       </c>
       <c r="H5" t="n">
-        <v>1.1363</v>
+        <v>0.7042</v>
       </c>
       <c r="I5" t="n">
-        <v>1.9842</v>
+        <v>0.4358</v>
       </c>
       <c r="J5" t="n">
-        <v>3.1709</v>
+        <v>0.8853</v>
       </c>
       <c r="K5" t="n">
-        <v>1.7957</v>
+        <v>0.8018999999999999</v>
       </c>
       <c r="L5" t="n">
-        <v>1.3753</v>
+        <v>0.0833</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.0505</v>
+        <v>0.2548</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.6594</v>
+        <v>-0.0977</v>
       </c>
       <c r="O5" t="n">
-        <v>0.6089</v>
+        <v>0.3525</v>
       </c>
       <c r="P5" t="n">
+        <v>-1.0995</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>-1.8326</v>
+      </c>
+      <c r="R5" t="n">
         <v>0.733</v>
       </c>
-      <c r="Q5" t="n">
-        <v>-0.3665</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.0995</v>
-      </c>
       <c r="S5" t="n">
-        <v>-0.7307</v>
+        <v>1.4427</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.4223</v>
+        <v>1.3043</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.3084</v>
+        <v>0.1384</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.6543</v>
+        <v>0.3219</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>0.3219</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.6543</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.3622</v>
+        <v>1.7031</v>
       </c>
       <c r="E6" t="n">
-        <v>0.4739</v>
+        <v>0.6662</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8883</v>
+        <v>1.0369</v>
       </c>
       <c r="G6" t="n">
         <v>1.0722</v>
@@ -922,13 +922,13 @@
         <v>1.4661</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.7991</v>
+        <v>-0.4581</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.4042</v>
+        <v>-0.2119</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.3949</v>
+        <v>-0.2462</v>
       </c>
       <c r="V6" t="n">
         <v>-0.0104</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.2968</v>
+        <v>1.4673</v>
       </c>
       <c r="E7" t="n">
-        <v>1.2706</v>
+        <v>1.3668</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0262</v>
+        <v>0.1005</v>
       </c>
       <c r="G7" t="n">
         <v>2.3204</v>
@@ -1000,13 +1000,13 @@
         <v>1.0995</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.5183</v>
+        <v>-0.3479</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.2021</v>
+        <v>-0.106</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.3162</v>
+        <v>-0.2419</v>
       </c>
       <c r="V7" t="n">
         <v>-0.3219</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7493</v>
+        <v>1.4065</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.2457</v>
+        <v>0.1389</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9951</v>
+        <v>1.2676</v>
       </c>
       <c r="G8" t="n">
         <v>-0.118</v>
@@ -1078,13 +1078,13 @@
         <v>1.2828</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.4051</v>
+        <v>0.2521</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.5324</v>
+        <v>-0.1478</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1274</v>
+        <v>0.3999</v>
       </c>
       <c r="V8" t="n">
         <v>-0.0104</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>S. CARRION BALLESTER</t>
+          <t>F. BLASCO MANZANO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.6335</v>
+        <v>-0.931</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.041</v>
+        <v>-1.4533</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4075</v>
+        <v>0.5223</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.1221</v>
+        <v>-2.5138</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.8435</v>
+        <v>-1.1035</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2787</v>
+        <v>-1.4103</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1649</v>
+        <v>-1.8206</v>
       </c>
       <c r="K9" t="n">
-        <v>0.6036</v>
+        <v>-0.09</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.4387</v>
+        <v>-1.7306</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.287</v>
+        <v>-0.6932</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.4471</v>
+        <v>-1.0136</v>
       </c>
       <c r="O9" t="n">
-        <v>0.16</v>
+        <v>0.3204</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.0995</v>
+        <v>0.5498</v>
       </c>
       <c r="Q9" t="n">
-        <v>-3.1154</v>
+        <v>-1.2828</v>
       </c>
       <c r="R9" t="n">
-        <v>2.0158</v>
+        <v>1.8326</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.6788</v>
+        <v>-0.234</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.6795</v>
+        <v>0.3831</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0005999999999999999</v>
+        <v>-0.6171</v>
       </c>
       <c r="V9" t="n">
         <v>1.267</v>
       </c>
       <c r="W9" t="n">
-        <v>1.5889</v>
+        <v>1.267</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.3219</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>F. BLASCO MANZANO</t>
+          <t>S. CARRION BALLESTER</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.6377</v>
+        <v>-1.5541</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.8379</v>
+        <v>-1.7386</v>
       </c>
       <c r="F10" t="n">
-        <v>0.2002</v>
+        <v>0.1845</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.5138</v>
+        <v>-1.1221</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.1035</v>
+        <v>-0.8435</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.4103</v>
+        <v>-0.2787</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.8206</v>
+        <v>0.1649</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.09</v>
+        <v>0.6036</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.7306</v>
+        <v>-0.4387</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.6932</v>
+        <v>-1.287</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.0136</v>
+        <v>-1.4471</v>
       </c>
       <c r="O10" t="n">
-        <v>0.3204</v>
+        <v>0.16</v>
       </c>
       <c r="P10" t="n">
-        <v>0.5498</v>
+        <v>-1.0995</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.2828</v>
+        <v>-3.1154</v>
       </c>
       <c r="R10" t="n">
-        <v>1.8326</v>
+        <v>2.0158</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.9406</v>
+        <v>-0.5994</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.0015</v>
+        <v>-0.3771</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.9391</v>
+        <v>-0.2223</v>
       </c>
       <c r="V10" t="n">
         <v>1.267</v>
       </c>
       <c r="W10" t="n">
-        <v>1.267</v>
+        <v>1.5889</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-0.3219</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.7718</v>
+        <v>-2.3129</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.6305</v>
+        <v>-2.2459</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.1413</v>
+        <v>-0.067</v>
       </c>
       <c r="G11" t="n">
         <v>-1.3711</v>
@@ -1312,13 +1312,13 @@
         <v>1.0995</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.317</v>
+        <v>0.142</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3311</v>
+        <v>0.0536</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0141</v>
+        <v>0.08840000000000001</v>
       </c>
       <c r="V11" t="n">
         <v>-1.267</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.5343</v>
+        <v>-4.4223</v>
       </c>
       <c r="E12" t="n">
-        <v>-6.1065</v>
+        <v>-6.5733</v>
       </c>
       <c r="F12" t="n">
-        <v>2.5722</v>
+        <v>2.1511</v>
       </c>
       <c r="G12" t="n">
         <v>-3.8856</v>
@@ -1390,13 +1390,13 @@
         <v>2.0158</v>
       </c>
       <c r="S12" t="n">
-        <v>1.4062</v>
+        <v>0.5183</v>
       </c>
       <c r="T12" t="n">
-        <v>0.4193</v>
+        <v>-0.0475</v>
       </c>
       <c r="U12" t="n">
-        <v>0.9869</v>
+        <v>0.5658</v>
       </c>
       <c r="V12" t="n">
         <v>-0.3219</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>8.867099999999999</v>
+        <v>9.4176</v>
       </c>
       <c r="E13" t="n">
-        <v>2.349000000000003</v>
+        <v>2.8996</v>
       </c>
       <c r="F13" t="n">
-        <v>6.5181</v>
+        <v>6.518099999999999</v>
       </c>
       <c r="G13" t="n">
         <v>7.213500000000002</v>
@@ -1438,7 +1438,7 @@
         <v>-1.2821</v>
       </c>
       <c r="I13" t="n">
-        <v>8.4955</v>
+        <v>8.495499999999996</v>
       </c>
       <c r="J13" t="n">
         <v>12.5045</v>
@@ -1450,13 +1450,13 @@
         <v>2.567200000000001</v>
       </c>
       <c r="M13" t="n">
-        <v>-5.290900000000001</v>
+        <v>-5.2909</v>
       </c>
       <c r="N13" t="n">
         <v>-11.2195</v>
       </c>
       <c r="O13" t="n">
-        <v>5.9284</v>
+        <v>5.928400000000001</v>
       </c>
       <c r="P13" t="n">
         <v>1.8326</v>
@@ -1468,13 +1468,13 @@
         <v>16.493</v>
       </c>
       <c r="S13" t="n">
-        <v>0.1846999999999996</v>
+        <v>0.7352999999999998</v>
       </c>
       <c r="T13" t="n">
-        <v>0.3508000000000004</v>
+        <v>0.9013</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.1661</v>
+        <v>-0.166</v>
       </c>
       <c r="V13" t="n">
         <v>-0.3635000000000001</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.2037</v>
+        <v>3.4549</v>
       </c>
       <c r="E14" t="n">
-        <v>3.956</v>
+        <v>2.4175</v>
       </c>
       <c r="F14" t="n">
-        <v>0.2477</v>
+        <v>1.0374</v>
       </c>
       <c r="G14" t="n">
         <v>-0.3229</v>
@@ -1546,13 +1546,13 @@
         <v>2.9321</v>
       </c>
       <c r="S14" t="n">
-        <v>2.1496</v>
+        <v>1.4008</v>
       </c>
       <c r="T14" t="n">
-        <v>2.2497</v>
+        <v>0.7112000000000001</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.1</v>
+        <v>0.6896</v>
       </c>
       <c r="V14" t="n">
         <v>1.2774</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.2557</v>
+        <v>2.7308</v>
       </c>
       <c r="E15" t="n">
-        <v>0.7705</v>
+        <v>0.9628</v>
       </c>
       <c r="F15" t="n">
-        <v>2.4852</v>
+        <v>1.768</v>
       </c>
       <c r="G15" t="n">
         <v>3.0848</v>
@@ -1624,13 +1624,13 @@
         <v>2.5656</v>
       </c>
       <c r="S15" t="n">
-        <v>2.1659</v>
+        <v>1.641</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.09420000000000001</v>
+        <v>0.09810000000000001</v>
       </c>
       <c r="U15" t="n">
-        <v>2.2601</v>
+        <v>1.5429</v>
       </c>
       <c r="V15" t="n">
         <v>0.0208</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.06569999999999999</v>
+        <v>-0.041</v>
       </c>
       <c r="E17" t="n">
         <v>-0.1435</v>
       </c>
       <c r="F17" t="n">
-        <v>0.07770000000000001</v>
+        <v>0.1025</v>
       </c>
       <c r="G17" t="n">
         <v>-0.2836</v>
@@ -1780,13 +1780,13 @@
         <v>0.3665</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.1486</v>
+        <v>-0.1239</v>
       </c>
       <c r="T17" t="n">
         <v>-0.1652</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0165</v>
+        <v>0.0413</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. CALANCHE GONZALEZ</t>
+          <t>J. TALLON GUIA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.7642</v>
+        <v>-0.1453</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.8491</v>
+        <v>0.3579</v>
       </c>
       <c r="F18" t="n">
-        <v>0.0848</v>
+        <v>-0.5032</v>
       </c>
       <c r="G18" t="n">
-        <v>0.6166</v>
+        <v>1.0658</v>
       </c>
       <c r="H18" t="n">
-        <v>0.6392</v>
+        <v>1.1428</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.0226</v>
+        <v>-0.077</v>
       </c>
       <c r="J18" t="n">
-        <v>1.2121</v>
+        <v>2.3056</v>
       </c>
       <c r="K18" t="n">
-        <v>1.1704</v>
+        <v>2.2541</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0417</v>
+        <v>0.0515</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.5955</v>
+        <v>-1.2398</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.5312</v>
+        <v>-1.1113</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.0643</v>
+        <v>-0.1285</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.9163</v>
+        <v>-0.3665</v>
       </c>
       <c r="Q18" t="n">
         <v>-1.8326</v>
       </c>
       <c r="R18" t="n">
-        <v>0.9163</v>
+        <v>1.4661</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.7865</v>
+        <v>0.412</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.5505</v>
+        <v>-0.1255</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.236</v>
+        <v>0.5375</v>
       </c>
       <c r="V18" t="n">
-        <v>0.3219</v>
+        <v>-1.2566</v>
       </c>
       <c r="W18" t="n">
-        <v>0.3219</v>
+        <v>0.0104</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-1.267</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. CONDE BARBERA</t>
+          <t>M. CALANCHE GONZALEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.9573</v>
+        <v>-0.2207</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.8612</v>
+        <v>-0.6567</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.0961</v>
+        <v>0.436</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.8181</v>
+        <v>0.6166</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.0745</v>
+        <v>0.6392</v>
       </c>
       <c r="I19" t="n">
-        <v>0.2564</v>
+        <v>-0.0226</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.641</v>
+        <v>1.2121</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.641</v>
+        <v>1.1704</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>0.0417</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.1771</v>
+        <v>-0.5955</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.4335</v>
+        <v>-0.5312</v>
       </c>
       <c r="O19" t="n">
-        <v>0.2564</v>
+        <v>-0.0643</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>-0.9163</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-1.8326</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>0.9163</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.1392</v>
+        <v>-0.243</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.2202</v>
+        <v>-0.3582</v>
       </c>
       <c r="U19" t="n">
-        <v>0.081</v>
+        <v>0.1152</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>0.3219</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>0.3219</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. CARRERAS GARRIGA</t>
+          <t>J. CONDE BARBERA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.4597</v>
+        <v>-0.8641</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.8547</v>
+        <v>-0.6689000000000001</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.605</v>
+        <v>-0.1952</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.5824</v>
+        <v>-0.8181</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.1752</v>
+        <v>-1.0745</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.4072</v>
+        <v>0.2564</v>
       </c>
       <c r="J20" t="n">
-        <v>0.1717</v>
+        <v>-0.641</v>
       </c>
       <c r="K20" t="n">
-        <v>0.13</v>
+        <v>-0.641</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0417</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.7541</v>
+        <v>-0.1771</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.3053</v>
+        <v>-0.4335</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.4489</v>
+        <v>0.2564</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.3665</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.9163</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.5498</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.1888</v>
+        <v>-0.046</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.1101</v>
+        <v>-0.0279</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.07870000000000001</v>
+        <v>-0.0181</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.3219</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.3219</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. TALLON GUIA</t>
+          <t>J. TORRES HERNANDO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.9738</v>
+        <v>-0.9474</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.5074</v>
+        <v>-1.0861</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.4663</v>
+        <v>0.1387</v>
       </c>
       <c r="G21" t="n">
-        <v>1.0658</v>
+        <v>-3.0106</v>
       </c>
       <c r="H21" t="n">
-        <v>1.1428</v>
+        <v>-0.2509</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.077</v>
+        <v>-2.7598</v>
       </c>
       <c r="J21" t="n">
-        <v>2.3056</v>
+        <v>-0.7753</v>
       </c>
       <c r="K21" t="n">
-        <v>2.2541</v>
+        <v>1.0864</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0515</v>
+        <v>-1.8617</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.2398</v>
+        <v>-2.2353</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.1113</v>
+        <v>-1.3373</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.1285</v>
+        <v>-0.898</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.3665</v>
+        <v>0.733</v>
       </c>
       <c r="Q21" t="n">
         <v>-1.8326</v>
       </c>
       <c r="R21" t="n">
-        <v>1.4661</v>
+        <v>2.5656</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.4165</v>
+        <v>0.3748</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.9909</v>
+        <v>-0.06710000000000001</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.4256</v>
+        <v>0.4419</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.2566</v>
+        <v>0.9554</v>
       </c>
       <c r="W21" t="n">
-        <v>0.0104</v>
+        <v>1.5889</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.267</v>
+        <v>-0.6335</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>F. TORCOLETTI</t>
+          <t>J. CARRERAS GARRIGA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.0293</v>
+        <v>-1.193</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.4185</v>
+        <v>-0.6624</v>
       </c>
       <c r="F22" t="n">
-        <v>0.3893</v>
+        <v>-0.5306999999999999</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.4591</v>
+        <v>-0.5824</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.0745</v>
+        <v>-0.1752</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.3846</v>
+        <v>-0.4072</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.2821</v>
+        <v>0.1717</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.641</v>
+        <v>0.13</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.641</v>
+        <v>0.0417</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.1771</v>
+        <v>-0.7541</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.4335</v>
+        <v>-0.3053</v>
       </c>
       <c r="O22" t="n">
-        <v>0.2564</v>
+        <v>-0.4489</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.5498</v>
+        <v>-0.3665</v>
       </c>
       <c r="Q22" t="n">
         <v>-0.9163</v>
       </c>
       <c r="R22" t="n">
-        <v>0.3665</v>
+        <v>0.5498</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.3319</v>
+        <v>0.0779</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.2202</v>
+        <v>0.0822</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1117</v>
+        <v>-0.0043</v>
       </c>
       <c r="V22" t="n">
-        <v>0.3115</v>
+        <v>-0.3219</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0.3115</v>
+        <v>-0.3219</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>J. TORRES HERNANDO</t>
+          <t>F. TORCOLETTI</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.4044</v>
+        <v>-1.8122</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.2784</v>
+        <v>-2.2262</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.126</v>
+        <v>0.4141</v>
       </c>
       <c r="G23" t="n">
-        <v>-3.0106</v>
+        <v>-1.4591</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.2509</v>
+        <v>-1.0745</v>
       </c>
       <c r="I23" t="n">
-        <v>-2.7598</v>
+        <v>-0.3846</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.7753</v>
+        <v>-1.2821</v>
       </c>
       <c r="K23" t="n">
-        <v>1.0864</v>
+        <v>-0.641</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.8617</v>
+        <v>-0.641</v>
       </c>
       <c r="M23" t="n">
-        <v>-2.2353</v>
+        <v>-0.1771</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.3373</v>
+        <v>-0.4335</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.898</v>
+        <v>0.2564</v>
       </c>
       <c r="P23" t="n">
-        <v>0.733</v>
+        <v>-0.5498</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.8326</v>
+        <v>-0.9163</v>
       </c>
       <c r="R23" t="n">
-        <v>2.5656</v>
+        <v>0.3665</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.0822</v>
+        <v>-0.1148</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.2594</v>
+        <v>-0.0279</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.8228</v>
+        <v>-0.08690000000000001</v>
       </c>
       <c r="V23" t="n">
-        <v>0.9554</v>
+        <v>0.3115</v>
       </c>
       <c r="W23" t="n">
-        <v>1.5889</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.6335</v>
+        <v>0.3115</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.1844</v>
+        <v>-2.8901</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.317</v>
+        <v>-3.6054</v>
       </c>
       <c r="F24" t="n">
-        <v>0.1325</v>
+        <v>0.7154</v>
       </c>
       <c r="G24" t="n">
         <v>-3.9408</v>
@@ -2326,13 +2326,13 @@
         <v>2.3823</v>
       </c>
       <c r="S24" t="n">
-        <v>0.479</v>
+        <v>0.7734</v>
       </c>
       <c r="T24" t="n">
-        <v>0.7119</v>
+        <v>0.4235</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.2329</v>
+        <v>0.3499</v>
       </c>
       <c r="V24" t="n">
         <v>0.6439</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-3.8129</v>
+        <v>-3.4181</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.34</v>
+        <v>-1.5323</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.4729</v>
+        <v>-1.8857</v>
       </c>
       <c r="G25" t="n">
         <v>-1.8882</v>
@@ -2404,13 +2404,13 @@
         <v>0.5498</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.8856000000000001</v>
+        <v>-0.4908</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.1847</v>
+        <v>-0.3771</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.7008</v>
+        <v>-0.1137</v>
       </c>
       <c r="V25" t="n">
         <v>-1.5889</v>
@@ -2437,25 +2437,25 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-8.8672</v>
+        <v>-5.021100000000001</v>
       </c>
       <c r="E26" t="n">
-        <v>-6.5182</v>
+        <v>-6.518199999999999</v>
       </c>
       <c r="F26" t="n">
-        <v>-2.3491</v>
+        <v>1.4973</v>
       </c>
       <c r="G26" t="n">
-        <v>-7.2134</v>
+        <v>-7.213400000000001</v>
       </c>
       <c r="H26" t="n">
-        <v>1.2821</v>
+        <v>1.282099999999999</v>
       </c>
       <c r="I26" t="n">
         <v>-8.4955</v>
       </c>
       <c r="J26" t="n">
-        <v>5.2911</v>
+        <v>5.291099999999998</v>
       </c>
       <c r="K26" t="n">
         <v>11.2196</v>
@@ -2467,7 +2467,7 @@
         <v>-12.5046</v>
       </c>
       <c r="N26" t="n">
-        <v>-9.937500000000002</v>
+        <v>-9.9375</v>
       </c>
       <c r="O26" t="n">
         <v>-2.567099999999999</v>
@@ -2482,13 +2482,13 @@
         <v>14.6606</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.1848000000000003</v>
+        <v>3.6614</v>
       </c>
       <c r="T26" t="n">
-        <v>0.1662</v>
+        <v>0.1661</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.3508999999999998</v>
+        <v>3.495299999999999</v>
       </c>
       <c r="V26" t="n">
         <v>0.3634999999999999</v>
